--- a/12622730.xlsx
+++ b/12622730.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b116aad2db31a879/Desktop/GIT/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{084834A7-55C9-40FB-8555-3568A5164B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F363908-B340-4917-9790-FF7885C472F4}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="8_{084834A7-55C9-40FB-8555-3568A5164B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A78CBC6-F7A9-4B4B-8399-287EB4DC32AB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4896" yWindow="1956" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -208,16 +208,34 @@
     <t>july</t>
   </si>
   <si>
-    <t>480 min</t>
-  </si>
-  <si>
-    <t>30 min</t>
-  </si>
-  <si>
     <t>MCA/D1P2632</t>
   </si>
   <si>
     <t>Neutral</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>happy</t>
+  </si>
+  <si>
+    <t>neutral</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>tired</t>
+  </si>
+  <si>
+    <t>satisfied</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>satisfed</t>
   </si>
 </sst>
 </file>
@@ -498,6 +516,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -922,7 +944,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -1076,7 +1098,7 @@
         <v>440</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L7" s="16" t="s">
         <v>50</v>
@@ -1089,137 +1111,250 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B8" s="14">
+        <v>540</v>
+      </c>
+      <c r="C8" s="14">
+        <v>90</v>
+      </c>
+      <c r="D8" s="14">
+        <v>90</v>
+      </c>
+      <c r="E8" s="14">
+        <v>30</v>
+      </c>
+      <c r="F8" s="14">
+        <v>200</v>
+      </c>
+      <c r="G8" s="14">
+        <v>5</v>
+      </c>
+      <c r="H8" s="14">
+        <v>400</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>90</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B9" s="14">
+        <v>400</v>
+      </c>
+      <c r="C9" s="14">
+        <v>40</v>
+      </c>
+      <c r="D9" s="14">
+        <v>100</v>
+      </c>
+      <c r="E9" s="14">
+        <v>20</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>200</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>760</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>680</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B10" s="14">
+        <v>600</v>
+      </c>
+      <c r="C10" s="14">
+        <v>50</v>
+      </c>
+      <c r="D10" s="14">
+        <v>120</v>
+      </c>
+      <c r="E10" s="14">
+        <v>20</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>100</v>
+      </c>
+      <c r="I10" s="15">
+        <v>890</v>
+      </c>
+      <c r="J10" s="15">
+        <f t="shared" si="1"/>
+        <v>550</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B11" s="14">
+        <v>450</v>
+      </c>
+      <c r="C11" s="14">
+        <v>10</v>
+      </c>
+      <c r="D11" s="14">
+        <v>120</v>
+      </c>
+      <c r="E11" s="14">
+        <v>10</v>
+      </c>
+      <c r="F11" s="14">
+        <v>200</v>
+      </c>
+      <c r="G11" s="14">
+        <v>5</v>
+      </c>
+      <c r="H11" s="14">
+        <v>100</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
+      <c r="A12" s="13">
+        <v>46266</v>
+      </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>10</v>
+      </c>
+      <c r="F12" s="14">
+        <v>200</v>
+      </c>
+      <c r="G12" s="14">
+        <v>6</v>
+      </c>
+      <c r="H12" s="14">
+        <v>200</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>530</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>910</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
+      <c r="A13" s="13">
+        <v>46267</v>
+      </c>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
+      <c r="D13" s="14">
+        <v>80</v>
+      </c>
       <c r="E13" s="14"/>
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>80</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1360</v>
       </c>
       <c r="K13" s="16"/>
       <c r="L13" s="16"/>

--- a/12622730.xlsx
+++ b/12622730.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b116aad2db31a879/Desktop/Activity/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{C875F731-EB5D-4018-B92E-DB6DE58EB0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{251142C7-0DC5-483B-93DF-63F81C6A6F6D}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{C875F731-EB5D-4018-B92E-DB6DE58EB0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{467497A0-D51E-4DA7-9EB7-A9F65781196B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2647,26 +2647,50 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B40" s="14">
+        <v>300</v>
+      </c>
+      <c r="C40" s="14">
+        <v>10</v>
+      </c>
+      <c r="D40" s="14">
+        <v>100</v>
+      </c>
+      <c r="E40" s="14">
+        <v>15</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>90</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>515</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>925</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>

--- a/12622730.xlsx
+++ b/12622730.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b116aad2db31a879/Desktop/Activity/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{C875F731-EB5D-4018-B92E-DB6DE58EB0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{467497A0-D51E-4DA7-9EB7-A9F65781196B}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{C875F731-EB5D-4018-B92E-DB6DE58EB0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18DD8288-59FE-487C-84FC-ED6358B43F00}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>August</t>
+  </si>
+  <si>
+    <t>noramal dayS</t>
   </si>
 </sst>
 </file>
@@ -2693,26 +2696,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B41" s="14">
+        <v>400</v>
+      </c>
+      <c r="C41" s="14">
+        <v>10</v>
+      </c>
+      <c r="D41" s="14">
+        <v>100</v>
+      </c>
+      <c r="E41" s="14">
+        <v>15</v>
+      </c>
+      <c r="F41" s="14">
+        <v>200</v>
+      </c>
+      <c r="G41" s="14">
+        <v>4</v>
+      </c>
+      <c r="H41" s="14">
+        <v>90</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>815</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>625</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>

--- a/12622730.xlsx
+++ b/12622730.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b116aad2db31a879/Desktop/Activity/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{C875F731-EB5D-4018-B92E-DB6DE58EB0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18DD8288-59FE-487C-84FC-ED6358B43F00}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{C875F731-EB5D-4018-B92E-DB6DE58EB0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8120EEDD-298E-4E64-8270-B10EF7F9C6DE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -588,6 +588,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2712,21 +2716,21 @@
         <v>15</v>
       </c>
       <c r="F41" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G41" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H41" s="14">
         <v>90</v>
       </c>
       <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v>815</v>
+        <v>615</v>
       </c>
       <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v>625</v>
+        <v>825</v>
       </c>
       <c r="K41" s="16" t="s">
         <v>49</v>
@@ -2742,26 +2746,50 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B42" s="14">
+        <v>400</v>
+      </c>
+      <c r="C42" s="14">
+        <v>15</v>
+      </c>
+      <c r="D42" s="14">
+        <v>100</v>
+      </c>
+      <c r="E42" s="14">
+        <v>15</v>
+      </c>
+      <c r="F42" s="14">
+        <v>250</v>
+      </c>
+      <c r="G42" s="14">
+        <v>5</v>
+      </c>
+      <c r="H42" s="14">
+        <v>90</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>

--- a/12622730.xlsx
+++ b/12622730.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b116aad2db31a879/Desktop/Activity/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{C875F731-EB5D-4018-B92E-DB6DE58EB0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8120EEDD-298E-4E64-8270-B10EF7F9C6DE}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="8_{C875F731-EB5D-4018-B92E-DB6DE58EB0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{228306DD-1747-4499-9A9D-B4497942D4F4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2792,26 +2792,48 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
+      <c r="A43" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B43" s="14">
+        <v>300</v>
+      </c>
+      <c r="C43" s="14">
+        <v>10</v>
+      </c>
+      <c r="D43" s="14">
+        <v>80</v>
+      </c>
+      <c r="E43" s="14">
+        <v>10</v>
+      </c>
+      <c r="F43" s="14">
+        <v>200</v>
+      </c>
+      <c r="G43" s="14">
+        <v>4</v>
+      </c>
       <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>840</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/12622730.xlsx
+++ b/12622730.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b116aad2db31a879/Desktop/Activity/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="8_{C875F731-EB5D-4018-B92E-DB6DE58EB0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{228306DD-1747-4499-9A9D-B4497942D4F4}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{8941C20E-10A0-44F0-AA14-95061146CA27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E17270F-E417-4622-B781-AB79CB79D062}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -202,9 +202,6 @@
     <t>ARCHANA A</t>
   </si>
   <si>
-    <t>8hr</t>
-  </si>
-  <si>
     <t>MCA/D1P2632</t>
   </si>
   <si>
@@ -299,6 +296,9 @@
   </si>
   <si>
     <t>noramal dayS</t>
+  </si>
+  <si>
+    <t>Excellent</t>
   </si>
 </sst>
 </file>
@@ -588,10 +588,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1016,7 +1012,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
@@ -1024,7 +1020,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G3" s="21"/>
     </row>
@@ -1094,8 +1090,8 @@
       <c r="A6" s="8">
         <v>46247</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>55</v>
+      <c r="B6" s="9">
+        <v>300</v>
       </c>
       <c r="C6" s="9">
         <v>30</v>
@@ -1117,11 +1113,11 @@
       </c>
       <c r="I6" s="10">
         <f t="shared" ref="I6:I79" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>290</v>
+        <v>590</v>
       </c>
       <c r="J6" s="10">
         <f t="shared" ref="J6:J79" si="1">IF(I6="","",1440-I6)</f>
-        <v>1150</v>
+        <v>850</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>49</v>
@@ -1176,10 +1172,10 @@
         <v>50</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1225,7 +1221,7 @@
         <v>51</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1262,16 +1258,16 @@
         <v>580</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1317,7 +1313,7 @@
         <v>51</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1363,7 +1359,7 @@
         <v>51</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1400,16 +1396,16 @@
         <v>895</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1452,10 +1448,10 @@
         <v>50</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1492,16 +1488,16 @@
         <v>390</v>
       </c>
       <c r="K14" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="M14" s="11" t="s">
-        <v>68</v>
-      </c>
       <c r="N14" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1538,16 +1534,16 @@
         <v>585</v>
       </c>
       <c r="K15" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M15" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="L15" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>68</v>
-      </c>
       <c r="N15" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1587,13 +1583,13 @@
         <v>49</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1630,7 +1626,7 @@
         <v>440</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L17" s="16" t="s">
         <v>50</v>
@@ -1639,7 +1635,7 @@
         <v>51</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1676,7 +1672,7 @@
         <v>90</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L18" s="16" t="s">
         <v>50</v>
@@ -1685,7 +1681,7 @@
         <v>51</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1722,16 +1718,16 @@
         <v>680</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L19" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M19" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M19" s="16" t="s">
-        <v>61</v>
-      </c>
       <c r="N19" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1767,16 +1763,16 @@
         <v>550</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M20" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="M20" s="16" t="s">
-        <v>63</v>
-      </c>
       <c r="N20" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1816,13 +1812,13 @@
         <v>49</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1859,16 +1855,16 @@
         <v>295</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1905,16 +1901,16 @@
         <v>210</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1951,16 +1947,16 @@
         <v>305</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -2000,13 +1996,13 @@
         <v>49</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -2043,16 +2039,16 @@
         <v>355</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M26" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M26" s="16" t="s">
-        <v>61</v>
-      </c>
       <c r="N26" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -2092,13 +2088,13 @@
         <v>49</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -2135,16 +2131,16 @@
         <v>65</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L28" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M28" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M28" s="16" t="s">
-        <v>61</v>
-      </c>
       <c r="N28" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2184,13 +2180,13 @@
         <v>49</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -2227,16 +2223,16 @@
         <v>240</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2273,16 +2269,16 @@
         <v>240</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -2319,16 +2315,16 @@
         <v>445</v>
       </c>
       <c r="K32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N32" s="17" t="s">
         <v>58</v>
-      </c>
-      <c r="L32" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="M32" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="N32" s="17" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -2365,16 +2361,16 @@
         <v>620</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2411,16 +2407,16 @@
         <v>480</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
@@ -2457,16 +2453,16 @@
         <v>440</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
@@ -2509,10 +2505,10 @@
         <v>50</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2549,16 +2545,16 @@
         <v>563</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L37" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M37" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
@@ -2601,15 +2597,15 @@
         <v>50</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B39" s="14">
         <v>400</v>
@@ -2641,16 +2637,16 @@
         <v>508</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
@@ -2693,10 +2689,10 @@
         <v>50</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
@@ -2742,7 +2738,7 @@
         <v>51</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
@@ -2779,7 +2775,7 @@
         <v>570</v>
       </c>
       <c r="K42" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L42" s="16" t="s">
         <v>50</v>
@@ -2788,7 +2784,7 @@
         <v>51</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
@@ -2813,17 +2809,19 @@
       <c r="G43" s="14">
         <v>4</v>
       </c>
-      <c r="H43" s="14"/>
+      <c r="H43" s="14">
+        <v>90</v>
+      </c>
       <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v>600</v>
+        <v>690</v>
       </c>
       <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v>840</v>
+        <v>750</v>
       </c>
       <c r="K43" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L43" s="16" t="s">
         <v>50</v>
@@ -2832,52 +2830,100 @@
         <v>51</v>
       </c>
       <c r="N43" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B44" s="14">
+        <v>500</v>
+      </c>
+      <c r="C44" s="14">
+        <v>10</v>
+      </c>
+      <c r="D44" s="14">
+        <v>70</v>
+      </c>
+      <c r="E44" s="14">
+        <v>10</v>
+      </c>
+      <c r="F44" s="14">
+        <v>400</v>
+      </c>
+      <c r="G44" s="14">
+        <v>8</v>
+      </c>
+      <c r="H44" s="14">
+        <v>50</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B45" s="14">
+        <v>400</v>
+      </c>
+      <c r="C45" s="14">
+        <v>10</v>
+      </c>
+      <c r="D45" s="14">
+        <v>60</v>
+      </c>
+      <c r="E45" s="14">
+        <v>15</v>
+      </c>
+      <c r="F45" s="14">
+        <v>200</v>
+      </c>
+      <c r="G45" s="14">
+        <v>4</v>
+      </c>
+      <c r="H45" s="14">
+        <v>50</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>735</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>705</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>
